--- a/docs/direct/direct-commander.xlsx
+++ b/docs/direct/direct-commander.xlsx
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -442,45 +442,50 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Тип объявления</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Доп. объявление группы</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Фраза (с минус-словами)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Ставка</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Заголовок 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Заголовок 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Текст 1</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Отображаемая ссылка</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Регион</t>
         </is>
@@ -497,43 +502,48 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>песня в подарок</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>60</v>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Песня в подарок за 10 минут</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>От 490 ₽, два варианта</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Расскажите про человека — получите песню с его именем. Текст бесплатно.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -548,25 +558,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>песня в подарок на заказ</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -577,25 +582,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>заказать песню в подарок</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>60</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -606,25 +606,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>песня на заказ</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>60</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -635,25 +630,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>заказать песню</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>60</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -664,25 +654,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>персональная песня</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>60</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,25 +678,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>именная песня в подарок</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>60</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -722,25 +702,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>песня с именем на заказ</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>60</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -751,25 +726,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>индивидуальная песня на заказ</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>60</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -780,25 +750,20 @@
           <t>Общие — песня в подарок</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>авторская песня на заказ</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>60</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -811,43 +776,48 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>песня в подарок маме</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>60</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>Песня маме за 10 минут</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>С её именем, от 490 ₽</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Напишите про маму три детали — песня будет про неё. Текст покажем бесплатно.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-mame/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -862,25 +832,20 @@
           <t>Кому — маме</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>песня для мамы на заказ</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>60</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -891,25 +856,20 @@
           <t>Кому — маме</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>песня маме на юбилей</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>60</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -920,25 +880,20 @@
           <t>Кому — маме</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>песня маме на день рождения заказать</t>
         </is>
       </c>
-      <c r="E15" t="n">
-        <v>60</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -949,25 +904,20 @@
           <t>Кому — маме</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>песня про маму на заказ</t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -980,43 +930,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>песня в подарок папе</t>
         </is>
       </c>
-      <c r="E17" t="n">
-        <v>60</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>60</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Песня папе или брату</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Можно с юмором, 490 ₽</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Его имя, его истории, его жанр. Текст показываем до записи — бесплатно.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-pape/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1031,25 +986,20 @@
           <t>Кому — папе и брату</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>песня для папы на заказ</t>
         </is>
       </c>
-      <c r="E18" t="n">
-        <v>60</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1060,25 +1010,20 @@
           <t>Кому — папе и брату</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>песня папе на юбилей</t>
         </is>
       </c>
-      <c r="E19" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1089,25 +1034,20 @@
           <t>Кому — папе и брату</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>песня в подарок брату</t>
         </is>
       </c>
-      <c r="E20" t="n">
-        <v>60</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1118,25 +1058,20 @@
           <t>Кому — папе и брату</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>песня брату на день рождения заказать</t>
         </is>
       </c>
-      <c r="E21" t="n">
-        <v>60</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1149,43 +1084,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>песня в подарок сыну</t>
         </is>
       </c>
-      <c r="E22" t="n">
-        <v>60</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>60</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>Песня ребёнку с его именем</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>За 10 минут, от 490 ₽</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Имя в припеве, любимые игрушки и дела. Текст бесплатно, песня за минуты.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-synu/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1200,25 +1140,20 @@
           <t>Кому — сыну и дочери</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>песня в подарок дочери</t>
         </is>
       </c>
-      <c r="E23" t="n">
-        <v>60</v>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1229,25 +1164,20 @@
           <t>Кому — сыну и дочери</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>детская песня с именем на заказ</t>
         </is>
       </c>
-      <c r="E24" t="n">
-        <v>60</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1258,25 +1188,20 @@
           <t>Кому — сыну и дочери</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>именная песня для ребенка</t>
         </is>
       </c>
-      <c r="E25" t="n">
-        <v>60</v>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1289,43 +1214,48 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>песня в подарок учителю</t>
         </is>
       </c>
-      <c r="E26" t="n">
-        <v>60</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>60</v>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>Песня учителю от класса</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>За 10 минут, от 490 ₽</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Имя, предмет и ваши школьные детали. Текст согласуете до записи.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-uchitelyu/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1340,25 +1270,20 @@
           <t>Кому — учителю</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>песня учителю от класса</t>
         </is>
       </c>
-      <c r="E27" t="n">
-        <v>60</v>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1369,25 +1294,20 @@
           <t>Кому — учителю</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>песня на день учителя на заказ</t>
         </is>
       </c>
-      <c r="E28" t="n">
-        <v>60</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1398,25 +1318,20 @@
           <t>Кому — учителю</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>песня на последний звонок на заказ</t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>60</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1429,43 +1344,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>песня на день рождения на заказ</t>
         </is>
       </c>
-      <c r="E30" t="n">
-        <v>60</v>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>60</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Песня на день рождения</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Успеете сегодня, 490 ₽</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Анкета три минуты, песня через десять. Работаем круглосуточно.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-na-den-rozhdeniya-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1480,25 +1400,20 @@
           <t>Повод — день рождения</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>заказать песню на день рождения</t>
         </is>
       </c>
-      <c r="E31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1509,25 +1424,20 @@
           <t>Повод — день рождения</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>поздравление песней на заказ</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>60</v>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1538,25 +1448,20 @@
           <t>Повод — день рождения</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>песня поздравление на заказ</t>
         </is>
       </c>
-      <c r="E33" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1569,43 +1474,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>песня на юбилей на заказ</t>
         </is>
       </c>
-      <c r="E34" t="n">
-        <v>60</v>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>60</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>Песня на юбилей за 10 минут</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Про жизнь, а не про годы</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Дело, семья и места — из ваших деталей. Два варианта звучания, от 490 ₽.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-na-70-let/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1620,25 +1530,20 @@
           <t>Повод — юбилей</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>песня на 70 лет юбилей</t>
         </is>
       </c>
-      <c r="E35" t="n">
-        <v>60</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1649,25 +1554,20 @@
           <t>Повод — юбилей</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>песня на 60 лет заказать</t>
         </is>
       </c>
-      <c r="E36" t="n">
-        <v>60</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1678,25 +1578,20 @@
           <t>Повод — юбилей</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>песня на 50 лет на заказ</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1707,25 +1602,20 @@
           <t>Повод — юбилей</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>музыкальный подарок на юбилей</t>
         </is>
       </c>
-      <c r="E38" t="n">
-        <v>60</v>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1738,43 +1628,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>сколько стоит песня на заказ</t>
         </is>
       </c>
-      <c r="E39" t="n">
-        <v>60</v>
-      </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>60</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>Песня на заказ — от 490 ₽</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Без доплат и звёздочек</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Три пакета, цены на странице. Текст бесплатно, платите после него.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/skolko-stoit-pesnya-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1789,25 +1684,20 @@
           <t>Цена</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>сколько стоит заказать песню</t>
         </is>
       </c>
-      <c r="E40" t="n">
-        <v>60</v>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1818,25 +1708,20 @@
           <t>Цена</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>песня на заказ цена</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>60</v>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1847,25 +1732,20 @@
           <t>Цена</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>песня в подарок цена</t>
         </is>
       </c>
-      <c r="E42" t="n">
-        <v>60</v>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1876,25 +1756,20 @@
           <t>Цена</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>песня на заказ недорого</t>
         </is>
       </c>
-      <c r="E43" t="n">
-        <v>60</v>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1907,43 +1782,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>написать песню на заказ</t>
         </is>
       </c>
-      <c r="E44" t="n">
-        <v>60</v>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>60</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>Напишем песню по вашей истории</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>Текст бесплатно, 490 ₽</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Сначала текст со структурой, потом запись. Правки не ограничены.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/napisat-pesnyu-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1958,25 +1838,20 @@
           <t>Написать текст</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>сочинить песню на заказ</t>
         </is>
       </c>
-      <c r="E45" t="n">
-        <v>60</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1987,25 +1862,20 @@
           <t>Написать текст</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>написать текст песни на заказ</t>
         </is>
       </c>
-      <c r="E46" t="n">
-        <v>60</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2016,25 +1886,20 @@
           <t>Написать текст</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>песня на заказ по вашему тексту</t>
         </is>
       </c>
-      <c r="E47" t="n">
-        <v>60</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2047,43 +1912,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Текстово-графическое</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>музыкальная открытка на заказ</t>
         </is>
       </c>
-      <c r="E48" t="n">
-        <v>60</v>
-      </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>60</v>
+      </c>
+      <c r="G48" t="inlineStr">
         <is>
           <t>Музыкальная открытка</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Песня и обложка, 890 ₽</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Отправляется одним сообщением. Готово через десять минут после анкеты.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/muzykalnaya-otkrytka-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -2098,25 +1968,20 @@
           <t>Музыкальная открытка</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>аудио поздравление на заказ</t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>60</v>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2127,25 +1992,20 @@
           <t>Музыкальная открытка</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>музыкальная открытка с именем</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>60</v>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2156,25 +2016,20 @@
           <t>Музыкальная открытка</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>песня открытка в подарок</t>
         </is>
       </c>
-      <c r="E51" t="n">
-        <v>60</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/direct/direct-commander.xlsx
+++ b/docs/direct/direct-commander.xlsx
@@ -413,20 +413,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,20 +477,40 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Заголовок 3</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Заголовок 4</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Текст 1</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Текст 2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Текст 3</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Отображаемая ссылка</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Регион</t>
         </is>
@@ -502,7 +527,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -525,25 +550,45 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>От 490 ₽, два варианта</t>
+          <t>Персональная песня на заказ</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Песня с именем вашего человека</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>От 490 ₽, два варианта на выбор</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Расскажите про человека — получите песню с его именем. Текст бесплатно.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Анкета три минуты, песня через десять. Работаем круглосуточно.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Сначала показываем текст, платите только если он вам нравится.</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -572,6 +617,16 @@
       <c r="F3" t="n">
         <v>60</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -596,6 +651,16 @@
       <c r="F4" t="n">
         <v>60</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -620,6 +685,16 @@
       <c r="F5" t="n">
         <v>60</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -644,6 +719,16 @@
       <c r="F6" t="n">
         <v>60</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -668,6 +753,16 @@
       <c r="F7" t="n">
         <v>60</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -692,6 +787,16 @@
       <c r="F8" t="n">
         <v>60</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -716,6 +821,16 @@
       <c r="F9" t="n">
         <v>60</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -740,6 +855,16 @@
       <c r="F10" t="n">
         <v>60</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -764,6 +889,16 @@
       <c r="F11" t="n">
         <v>60</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -776,7 +911,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -799,25 +934,45 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>С её именем, от 490 ₽</t>
+          <t>Песня в подарок маме на юбилей</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Напишите про маму три детали — песня будет про неё. Текст покажем бесплатно.</t>
+          <t>Песня про вашу маму, с её именем</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>Маме — песня от 490 ₽</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Напишите про маму три детали — песня будет про неё. Текст бесплатно.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Дача, пироги, её фраза — из этого и получается песня, а не открытка.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Два варианта звучания, MP3. Успеете даже если юбилей сегодня.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-mame/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -846,6 +1001,16 @@
       <c r="F13" t="n">
         <v>60</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -870,6 +1035,16 @@
       <c r="F14" t="n">
         <v>60</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -894,6 +1069,16 @@
       <c r="F15" t="n">
         <v>60</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -918,6 +1103,16 @@
       <c r="F16" t="n">
         <v>60</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -930,7 +1125,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -953,25 +1148,45 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Можно с юмором, 490 ₽</t>
+          <t>Песня в подарок папе на заказ</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Брату — песня, можно с юмором</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>От 490 ₽, готово за 10 минут</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>Его имя, его истории, его жанр. Текст показываем до записи — бесплатно.</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Без пафоса: про гараж, рыбалку и фразу, которую он повторяет.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Рок, рэп или акустика — выберите звучание, которое он слушает сам.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-pape/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1000,6 +1215,16 @@
       <c r="F18" t="n">
         <v>60</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1024,6 +1249,16 @@
       <c r="F19" t="n">
         <v>60</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1048,6 +1283,16 @@
       <c r="F20" t="n">
         <v>60</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1072,6 +1317,16 @@
       <c r="F21" t="n">
         <v>60</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1084,7 +1339,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1107,25 +1362,45 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>За 10 минут, от 490 ₽</t>
+          <t>Именная песня для сына или дочери</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>Детская песня на заказ за 10 минут</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>От 490 ₽, два варианта</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>Имя в припеве, любимые игрушки и дела. Текст бесплатно, песня за минуты.</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Ребёнок узнаёт своё имя и просит включить ещё раз. И ещё раз.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Для малыша — весёлая и ритмичная, взрослому сыну — спокойная и честная.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-synu/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1154,6 +1429,16 @@
       <c r="F23" t="n">
         <v>60</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1178,6 +1463,16 @@
       <c r="F24" t="n">
         <v>60</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1202,6 +1497,16 @@
       <c r="F25" t="n">
         <v>60</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1214,7 +1519,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1237,25 +1542,45 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>За 10 минут, от 490 ₽</t>
+          <t>Подарок учителю, который не передарят</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Имя, предмет и ваши школьные детали. Текст согласуете до записи.</t>
+          <t>Песня на последний звонок</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>От 490 ₽, готово за 10 минут</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Имя, предмет и ваши школьные детали. Текст читаете до записи.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Соберите детали всем классом — песню узнает вся параллель.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Цветы забудутся, запись останется на телефоне на годы.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-uchitelyu/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1284,6 +1609,16 @@
       <c r="F27" t="n">
         <v>60</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1308,6 +1643,16 @@
       <c r="F28" t="n">
         <v>60</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1332,6 +1677,16 @@
       <c r="F29" t="n">
         <v>60</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1344,7 +1699,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1367,25 +1722,45 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Успеете сегодня, 490 ₽</t>
+          <t>Успеете, даже если праздник сегодня</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
+          <t>Поздравление песней на заказ</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>От 490 ₽ за десять минут</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>Анкета три минуты, песня через десять. Работаем круглосуточно.</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Включите её вместо тоста — и в комнате станет тихо.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Два варианта звучания на один текст: выбираете тот, что ближе.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-na-den-rozhdeniya-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1414,6 +1789,16 @@
       <c r="F31" t="n">
         <v>60</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1438,6 +1823,16 @@
       <c r="F32" t="n">
         <v>60</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1462,6 +1857,16 @@
       <c r="F33" t="n">
         <v>60</v>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1474,7 +1879,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1497,25 +1902,45 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Про жизнь, а не про годы</t>
+          <t>Песня на 70 лет: про жизнь, а не про годы</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Дело, семья и места — из ваших деталей. Два варианта звучания, от 490 ₽.</t>
+          <t>Музыкальный подарок на юбилей</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>От 490 ₽, два варианта</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Дело, семья и места — из ваших деталей. Тёплое звучание, живые инструменты.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Имена детей и внуков прозвучат в песне — каждый услышит своё.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Про шутки о возрасте не переживайте: таких строк в тексте не будет.</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
           <t>https://genius-bot.ru/pesnya-na-70-let/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1544,6 +1969,16 @@
       <c r="F35" t="n">
         <v>60</v>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1568,6 +2003,16 @@
       <c r="F36" t="n">
         <v>60</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1592,6 +2037,16 @@
       <c r="F37" t="n">
         <v>60</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1616,6 +2071,16 @@
       <c r="F38" t="n">
         <v>60</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1628,7 +2093,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1651,25 +2116,45 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Без доплат и звёздочек</t>
+          <t>Сколько стоит песня в подарок</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Три пакета, цены на странице. Текст бесплатно, платите после него.</t>
+          <t>Три пакета, цены без звёздочек</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>Текст бесплатно, платите после</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>490 ₽ песня, 890 ₽ с обложкой, 1390 ₽ с клипом. Доплат нет.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Сначала читаете текст, потом решаете, платить ли. Это бесплатно.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>В студии это стоит от 4000 ₽ и делается сутки. У нас — десять минут.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
           <t>https://genius-bot.ru/skolko-stoit-pesnya-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1698,6 +2183,16 @@
       <c r="F40" t="n">
         <v>60</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1722,6 +2217,16 @@
       <c r="F41" t="n">
         <v>60</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1746,6 +2251,16 @@
       <c r="F42" t="n">
         <v>60</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1770,6 +2285,16 @@
       <c r="F43" t="n">
         <v>60</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1782,7 +2307,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1805,25 +2330,45 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Текст бесплатно, 490 ₽</t>
+          <t>Написать песню на заказ</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Сначала текст со структурой, потом запись. Правки не ограничены.</t>
+          <t>Текст песни бесплатно, сразу</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>Сочиним и запишем за 10 минут</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Сначала текст со структурой, потом запись. Пересобрать можно бесплатно.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Перечислите детали списком — рифмовать самому не нужно.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Можно заказать только текст: споёте его сами или у нас.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>https://genius-bot.ru/napisat-pesnyu-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1852,6 +2397,16 @@
       <c r="F45" t="n">
         <v>60</v>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1876,6 +2431,16 @@
       <c r="F46" t="n">
         <v>60</v>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1900,6 +2465,16 @@
       <c r="F47" t="n">
         <v>60</v>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1912,7 +2487,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Текстово-графическое</t>
+          <t>Комбинаторное</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1930,30 +2505,50 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Музыкальная открытка</t>
+          <t>Музыкальная открытка на заказ</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Песня и обложка, 890 ₽</t>
+          <t>Открытка, которая звучит</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Отправляется одним сообщением. Готово через десять минут после анкеты.</t>
+          <t>Песня и обложка — 890 ₽</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>Готово через 10 минут</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Отправляется одним сообщением в любой город. Ничего не нужно везти.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Песня с именем, картинка и текст файлом — всё остаётся у вас навсегда.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Забыли поздравить вовремя? Такая открытка спасает лучше слов.</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>https://genius-bot.ru/muzykalnaya-otkrytka-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1982,6 +2577,16 @@
       <c r="F49" t="n">
         <v>60</v>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2006,6 +2611,16 @@
       <c r="F50" t="n">
         <v>60</v>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2030,6 +2645,16 @@
       <c r="F51" t="n">
         <v>60</v>
       </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/direct/direct-commander.xlsx
+++ b/docs/direct/direct-commander.xlsx
@@ -413,25 +413,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="46" customWidth="1" min="11" max="11"/>
-    <col width="46" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
     <col width="46" customWidth="1" min="13" max="13"/>
-    <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="46" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,55 +464,65 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Минус-фразы на группу</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Минус-фразы на кампанию</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Ставка</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Заголовок 1</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Заголовок 2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Заголовок 3</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Заголовок 4</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Текст 1</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Текст 2</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Текст 3</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Ссылка</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Отображаемая ссылка</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Регион</t>
         </is>
@@ -527,7 +539,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -537,58 +549,68 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>песня в подарок</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>60</v>
+          <t>"песня в подарок"</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>группа, коллектив, хор, ноты, кавер, петь самому, обучение, курсы</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Песня в подарок за 10 минут</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Персональная песня на заказ</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Песня с именем вашего человека</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>От 490 ₽, два варианта на выбор</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Genius-bot: песня от 490 ₽</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>Расскажите про человека — получите песню с его именем. Текст бесплатно.</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Анкета три минуты, песня через десять. Работаем круглосуточно.</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Сначала показываем текст, платите только если он вам нравится.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -611,14 +633,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>песня в подарок на заказ</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня в подарок на заказ"</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>60</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -627,6 +649,8 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -645,14 +669,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>заказать песню в подарок</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>60</v>
-      </c>
+          <t>"заказать песню в подарок"</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>60</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -661,6 +685,8 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -679,14 +705,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>песня на заказ</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на заказ"</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>60</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -695,6 +721,8 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -713,14 +741,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>заказать песню</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>60</v>
-      </c>
+          <t>"заказать песню"</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>60</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -729,6 +757,8 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -747,14 +777,14 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>персональная песня</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>60</v>
-      </c>
+          <t>"персональная песня"</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>60</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -763,6 +793,8 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -781,14 +813,14 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>именная песня в подарок</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>60</v>
-      </c>
+          <t>"именная песня в подарок"</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>60</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -797,6 +829,8 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -815,14 +849,14 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>песня с именем на заказ</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня с именем на заказ"</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>60</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -831,6 +865,8 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -849,14 +885,14 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>индивидуальная песня на заказ</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>60</v>
-      </c>
+          <t>"индивидуальная песня на заказ"</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>60</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -865,6 +901,8 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -883,14 +921,14 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>авторская песня на заказ</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>60</v>
-      </c>
+          <t>"авторская песня на заказ"</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>60</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -899,6 +937,8 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -911,7 +951,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -921,58 +961,68 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>песня в подарок маме</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>60</v>
+          <t>"песня в подарок маме"</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>мама анархия, мамба, мамма мия, детский сад, сценарий, стихи</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>60</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>Песня маме за 10 минут</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Песня в подарок маме на юбилей</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Песня про вашу маму, с её именем</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Маме — песня от 490 ₽</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Genius-bot: маме от 490 ₽</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>Напишите про маму три детали — песня будет про неё. Текст бесплатно.</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Дача, пироги, её фраза — из этого и получается песня, а не открытка.</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Два варианта звучания, MP3. Успеете даже если юбилей сегодня.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-mame/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -995,14 +1045,14 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>песня для мамы на заказ</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня для мамы на заказ"</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>60</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -1011,6 +1061,8 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1029,14 +1081,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>песня маме на юбилей</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня маме на юбилей"</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>60</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1045,6 +1097,8 @@
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1063,14 +1117,14 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>песня маме на день рождения заказать</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня маме на день рождения заказать"</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>60</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1079,6 +1133,8 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1097,14 +1153,14 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>песня про маму на заказ</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня про маму на заказ"</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>60</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1113,6 +1169,8 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1125,7 +1183,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1135,58 +1193,68 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>песня в подарок папе</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>60</v>
+          <t>"песня в подарок папе"</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>брат за брата, сериал, тост, сценарий, стихи, поздравление скачать</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>60</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>Песня папе или брату</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Песня в подарок папе на заказ</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Брату — песня, можно с юмором</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>От 490 ₽, готово за 10 минут</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Genius-bot: от 490 ₽ за 10 минут</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>Его имя, его истории, его жанр. Текст показываем до записи — бесплатно.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Без пафоса: про гараж, рыбалку и фразу, которую он повторяет.</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Рок, рэп или акустика — выберите звучание, которое он слушает сам.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-pape/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1209,14 +1277,14 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>песня для папы на заказ</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня для папы на заказ"</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>60</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1225,6 +1293,8 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1243,14 +1313,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>песня папе на юбилей</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня папе на юбилей"</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>60</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1259,6 +1329,8 @@
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1277,14 +1349,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>песня в подарок брату</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня в подарок брату"</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>60</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1293,6 +1365,8 @@
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1311,14 +1385,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>песня брату на день рождения заказать</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня брату на день рождения заказать"</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>60</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1327,6 +1401,8 @@
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1339,7 +1415,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1349,58 +1425,68 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>песня в подарок сыну</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>60</v>
+          <t>"песня в подарок сыну"</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>колыбельная слушать, мультфильм, утренник, сценарий, ноты, минусовки детские</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>60</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>Песня ребёнку с его именем</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Именная песня для сына или дочери</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Детская песня на заказ за 10 минут</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>От 490 ₽, два варианта</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Genius-bot: детям от 490 ₽</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>Имя в припеве, любимые игрушки и дела. Текст бесплатно, песня за минуты.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Ребёнок узнаёт своё имя и просит включить ещё раз. И ещё раз.</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Для малыша — весёлая и ритмичная, взрослому сыну — спокойная и честная.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-synu/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1423,14 +1509,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>песня в подарок дочери</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня в подарок дочери"</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>60</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1439,6 +1525,8 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1457,14 +1545,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>детская песня с именем на заказ</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>60</v>
-      </c>
+          <t>"детская песня с именем на заказ"</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>60</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1473,6 +1561,8 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1491,14 +1581,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>именная песня для ребенка</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>60</v>
-      </c>
+          <t>"именная песня для ребенка"</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>60</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -1507,6 +1597,8 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1519,7 +1611,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1529,58 +1621,68 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>песня в подарок учителю</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>60</v>
+          <t>"песня в подарок учителю"</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>сценарий, переделка текст, минусовка, флешмоб, готовые песни, скачать текст</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>60</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>Песня учителю от класса</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Подарок учителю, который не передарят</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Песня на последний звонок</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>От 490 ₽, готово за 10 минут</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Genius-bot: от 490 ₽ за 10 минут</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>Имя, предмет и ваши школьные детали. Текст читаете до записи.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Соберите детали всем классом — песню узнает вся параллель.</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Цветы забудутся, запись останется на телефоне на годы.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-v-podarok-uchitelyu/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1603,14 +1705,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>песня учителю от класса</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня учителю от класса"</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>60</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1619,6 +1721,8 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1637,14 +1741,14 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>песня на день учителя на заказ</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на день учителя на заказ"</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>60</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1653,6 +1757,8 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1671,14 +1777,14 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>песня на последний звонок на заказ</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на последний звонок на заказ"</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>60</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1687,6 +1793,8 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1699,7 +1807,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1709,58 +1817,68 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>песня на день рождения на заказ</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>60</v>
+          <t>"песня на день рождения на заказ"</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>хэппи бездей, happy birthday, тамада, ведущий, сценарий, шары, торт</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>60</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>Песня на день рождения</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Успеете, даже если праздник сегодня</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Поздравление песней на заказ</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>От 490 ₽ за десять минут</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Genius-bot: от 490 ₽ за 10 минут</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>Анкета три минуты, песня через десять. Работаем круглосуточно.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Включите её вместо тоста — и в комнате станет тихо.</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>Два варианта звучания на один текст: выбираете тот, что ближе.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-na-den-rozhdeniya-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1783,14 +1901,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>заказать песню на день рождения</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>60</v>
-      </c>
+          <t>"заказать песню на день рождения"</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>60</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1799,6 +1917,8 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1817,14 +1937,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>поздравление песней на заказ</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>60</v>
-      </c>
+          <t>"поздравление песней на заказ"</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>60</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1833,6 +1953,8 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1851,14 +1973,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>песня поздравление на заказ</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня поздравление на заказ"</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>60</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -1867,6 +1989,8 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1879,7 +2003,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1889,58 +2013,68 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>песня на юбилей на заказ</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>60</v>
+          <t>"песня на юбилей на заказ"</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>сценарий, тамада, ведущий, банкет, ресторан, переделка текст, минусовка</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>60</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>Песня на юбилей за 10 минут</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Песня на 70 лет: про жизнь, а не про годы</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Музыкальный подарок на юбилей</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>От 490 ₽, два варианта</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Genius-bot: от 490 ₽, два варианта</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>Дело, семья и места — из ваших деталей. Тёплое звучание, живые инструменты.</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Имена детей и внуков прозвучат в песне — каждый услышит своё.</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>Про шутки о возрасте не переживайте: таких строк в тексте не будет.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/pesnya-na-70-let/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -1963,14 +2097,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>песня на 70 лет юбилей</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на 70 лет юбилей"</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>60</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -1979,6 +2113,8 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1997,14 +2133,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>песня на 60 лет заказать</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на 60 лет заказать"</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>60</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -2013,6 +2149,8 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2031,14 +2169,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>песня на 50 лет на заказ</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на 50 лет на заказ"</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>60</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -2047,6 +2185,8 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2065,14 +2205,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>музыкальный подарок на юбилей</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>60</v>
-      </c>
+          <t>"музыкальный подарок на юбилей"</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>60</v>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -2081,6 +2221,8 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2093,7 +2235,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2103,58 +2245,68 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>сколько стоит песня на заказ</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>60</v>
+          <t>"сколько стоит песня на заказ"</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>студия аренда, час записи, прайс студии, сведение, мастеринг, обучение</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>60</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>Песня на заказ — от 490 ₽</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Сколько стоит песня в подарок</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Три пакета, цены без звёздочек</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Текст бесплатно, платите после</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Genius-bot: текст бесплатно</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>490 ₽ песня, 890 ₽ с обложкой, 1390 ₽ с клипом. Доплат нет.</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Сначала читаете текст, потом решаете, платить ли. Это бесплатно.</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>В студии это стоит от 4000 ₽ и делается сутки. У нас — десять минут.</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/skolko-stoit-pesnya-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -2177,14 +2329,14 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>сколько стоит заказать песню</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>60</v>
-      </c>
+          <t>"сколько стоит заказать песню"</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>60</v>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -2193,6 +2345,8 @@
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2211,14 +2365,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>песня на заказ цена</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на заказ цена"</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>60</v>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2227,6 +2381,8 @@
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2245,14 +2401,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>песня в подарок цена</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня в подарок цена"</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>60</v>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2261,6 +2417,8 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2279,14 +2437,14 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>песня на заказ недорого</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на заказ недорого"</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>60</v>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2295,6 +2453,8 @@
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2307,7 +2467,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2317,58 +2477,68 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>написать песню на заказ</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>60</v>
+          <t>"написать песню на заказ"</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>как научиться, урок, правила, рифма подобрать, генератор рифм, курсы</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>60</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>Напишем песню по вашей истории</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Написать песню на заказ</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Текст песни бесплатно, сразу</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Сочиним и запишем за 10 минут</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Genius-bot: сочиним за 10 минут</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>Сначала текст со структурой, потом запись. Пересобрать можно бесплатно.</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Перечислите детали списком — рифмовать самому не нужно.</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Можно заказать только текст: споёте его сами или у нас.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/napisat-pesnyu-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -2391,14 +2561,14 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>сочинить песню на заказ</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>60</v>
-      </c>
+          <t>"сочинить песню на заказ"</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>60</v>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2407,6 +2577,8 @@
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2425,14 +2597,14 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>написать текст песни на заказ</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>60</v>
-      </c>
+          <t>"написать текст песни на заказ"</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>60</v>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2441,6 +2613,8 @@
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2459,14 +2633,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>песня на заказ по вашему тексту</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня на заказ по вашему тексту"</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>60</v>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2475,6 +2649,8 @@
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2487,7 +2663,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Комбинаторное</t>
+          <t>Комбинаторное объявление</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2497,58 +2673,68 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>музыкальная открытка на заказ</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>60</v>
+          <t>"музыкальная открытка на заказ"</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>бумажная, купить открытку, шаблон, распечатать, своими руками, картинка скачать</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>скачать, слушать, бесплатно, минус, минусовка, караоке, аккорды, ноты, текст песни, слова песни, ремикс, mp3, торрент, ютуб, видео скачать, советские, ссср, конкурс, работа, вакансия, реферат</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>60</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>Музыкальная открытка на заказ</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Открытка, которая звучит</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Песня и обложка — 890 ₽</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Готово через 10 минут</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Genius-bot: готово за 10 минут</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>Отправляется одним сообщением в любой город. Ничего не нужно везти.</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Песня с именем, картинка и текст файлом — всё остаётся у вас навсегда.</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Забыли поздравить вовремя? Такая открытка спасает лучше слов.</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://genius-bot.ru/muzykalnaya-otkrytka-na-zakaz/?utm_source=yandex&amp;utm_medium=cpc&amp;utm_campaign=podarok&amp;utm_term={keyword}&amp;utm_content={ad_id}</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>pesnya-v-podarok</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>Россия</t>
         </is>
@@ -2571,14 +2757,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>аудио поздравление на заказ</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>60</v>
-      </c>
+          <t>"аудио поздравление на заказ"</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>60</v>
+      </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2587,6 +2773,8 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2605,14 +2793,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>музыкальная открытка с именем</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>60</v>
-      </c>
+          <t>"музыкальная открытка с именем"</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>60</v>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2621,6 +2809,8 @@
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2639,14 +2829,14 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>песня открытка в подарок</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>60</v>
-      </c>
+          <t>"песня открытка в подарок"</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>60</v>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2655,6 +2845,8 @@
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
